--- a/documentos/Registro de ventas.xlsx
+++ b/documentos/Registro de ventas.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoja1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja1'!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja1'!$A$3:$K$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,8 +18,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,10 +33,33 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001F2933"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001E7A46"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00B03A2E"/>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -43,11 +68,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="001B3A4B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7F0F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -55,28 +95,75 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
     <border>
       <left style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00D5DEE7"/>
       </left>
       <right style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00D5DEE7"/>
       </right>
       <top style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00D5DEE7"/>
       </top>
       <bottom style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00D5DEE7"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -440,85 +527,1087 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E79"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="38" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Registro de ventas</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="10" customHeight="1"/>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
           <t>Vendedor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Región</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Producto</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Ventas</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Meta</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Satisfacción (%)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Devolución</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Cumplimiento</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Tipo de venta</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Revisión de ventas</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>Clasificación de venta</t>
         </is>
       </c>
     </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>13000</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>Meta alcanzada</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Venta destacada</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Correcta</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Tablet</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>9800</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" s="15" t="inlineStr">
+        <is>
+          <t>Meta no alcanzada</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>Venta normal</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>21000</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>Meta alcanzada</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Venta destacada</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>Correcta</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>Excelente</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>María</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>7500</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>9000</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="15" t="inlineStr">
+        <is>
+          <t>Meta no alcanzada</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Venta normal</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Pedro</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>16500</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>Meta alcanzada</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Venta destacada</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Correcta</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Sofía</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Tablet</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>13300</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G9" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="16" t="inlineStr">
+        <is>
+          <t>Meta alcanzada</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Venta normal</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>Correcta</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Diego</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>6800</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>8500</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" s="17" t="inlineStr">
+        <is>
+          <t>Meta no alcanzada</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>Venta normal</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Laura</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>22500</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="16" t="inlineStr">
+        <is>
+          <t>Meta alcanzada</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>Venta destacada</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>Correcta</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>Excelente</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Jorge</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Bajío</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Tablet</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>11200</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>13000</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" s="17" t="inlineStr">
+        <is>
+          <t>Meta no alcanzada</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>Venta normal</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>Correcta</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Fernanda</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>9200</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>11000</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t>Meta no alcanzada</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Venta normal</t>
+        </is>
+      </c>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="K13" s="10" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Ricardo</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Golfo</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>14300</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>16000</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" s="17" t="inlineStr">
+        <is>
+          <t>Meta no alcanzada</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>Venta normal</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Valeria</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Noroeste</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>19800</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="16" t="inlineStr">
+        <is>
+          <t>Meta alcanzada</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Venta destacada</t>
+        </is>
+      </c>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>Correcta</t>
+        </is>
+      </c>
+      <c r="K15" s="10" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Sureste</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Tablet</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>7600</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" s="17" t="inlineStr">
+        <is>
+          <t>Meta no alcanzada</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>Venta normal</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Paola</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Bajío</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>10400</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G17" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="15" t="inlineStr">
+        <is>
+          <t>Meta no alcanzada</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>Venta destacada</t>
+        </is>
+      </c>
+      <c r="J17" s="10" t="inlineStr">
+        <is>
+          <t>Correcta</t>
+        </is>
+      </c>
+      <c r="K17" s="10" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Andrés</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>17200</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>16000</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>Meta alcanzada</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>Venta destacada</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>Correcta</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Daniela</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Tablet</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>12100</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>14000</v>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G19" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" s="15" t="inlineStr">
+        <is>
+          <t>Meta no alcanzada</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>Venta destacada</t>
+        </is>
+      </c>
+      <c r="J19" s="10" t="inlineStr">
+        <is>
+          <t>Correcta</t>
+        </is>
+      </c>
+      <c r="K19" s="10" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Héctor</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Golfo</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>8900</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>10500</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G20" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="17" t="inlineStr">
+        <is>
+          <t>Meta no alcanzada</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>Venta normal</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>Correcta</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Camila</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>Noreste</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>21400</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="16" t="inlineStr">
+        <is>
+          <t>Meta alcanzada</t>
+        </is>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>Venta destacada</t>
+        </is>
+      </c>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>Correcta</t>
+        </is>
+      </c>
+      <c r="K21" s="10" t="inlineStr">
+        <is>
+          <t>Excelente</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Bruno</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Tablet</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>8700</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>11000</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G22" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H22" s="17" t="inlineStr">
+        <is>
+          <t>Meta no alcanzada</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>Venta normal</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Renata</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="n">
+        <v>15600</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>14500</v>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G23" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="16" t="inlineStr">
+        <is>
+          <t>Meta alcanzada</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>Venta normal</t>
+        </is>
+      </c>
+      <c r="J23" s="10" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="K23" s="10" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+  <autoFilter ref="A3:K23"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="3" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>